--- a/table4_all_models.xlsx
+++ b/table4_all_models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\27261\Desktop\3_Courses in PHBS\3_09_AppliedStochasticProcess\Project_sv32_EMC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120CD47E-CA58-4970-A458-9136E0DE8780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F480BAC7-8783-47DA-A490-F7A219CB2288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,23 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="148">
   <si>
     <t>Exact Simulation</t>
   </si>
   <si>
-    <t>Exact Simulation(Use Fourier-Cosine)</t>
-  </si>
-  <si>
-    <t>Exact Simulation(Use Moment Matching)</t>
-  </si>
-  <si>
-    <t>Almost Exact Simulation(Inverse Gaussian)</t>
-  </si>
-  <si>
-    <t>Almost Exact Simulation(Gamma)</t>
-  </si>
-  <si>
     <t>Fast Fourier Transformation</t>
   </si>
   <si>
@@ -464,6 +452,26 @@
   </si>
   <si>
     <t>0.0002768 (0.05%)</t>
+  </si>
+  <si>
+    <t>Exact Simulation
+(Use Fourier-Cosine)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exact Simulation
+(Use Moment Matching)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Almost Exact Simulation
+(Inverse Gaussian)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Almost Exact Simulation
+(Gamma)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -565,21 +573,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -882,1261 +904,1456 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.1328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.06640625" style="9"/>
+    <col min="3" max="3" width="11.1328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="10.06640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.06640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.06640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.06640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.06640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.06640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B1" s="1"/>
+    <row r="1" spans="1:12" s="9" customFormat="1" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="4" t="s">
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="7"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
         <v>85</v>
       </c>
       <c r="C4" s="2">
         <v>55.271879900014028</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E4" s="2">
         <v>21.933501299936321</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G4" s="2">
         <v>3.7690300028771162E-2</v>
       </c>
-      <c r="H4" t="s">
-        <v>13</v>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="I4" s="2">
         <v>0.38373500015586609</v>
       </c>
-      <c r="J4" t="s">
-        <v>14</v>
+      <c r="J4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="K4" s="2">
         <v>0.35061750002205372</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="3">
+        <v>98</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="2">
-        <v>0.25195700000040228</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="2">
-        <v>6.4450300065800548E-2</v>
-      </c>
-      <c r="P4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="1">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" t="s">
+    </row>
+    <row r="6" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="3">
+        <v>100</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" t="s">
+      <c r="K6" s="2"/>
+      <c r="L6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="1">
-        <v>100</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" t="s">
+    </row>
+    <row r="7" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="3">
+        <v>102</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="3"/>
-      <c r="N6" t="s">
+      <c r="K7" s="2"/>
+      <c r="L7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="1">
-        <v>102</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" t="s">
+    </row>
+    <row r="8" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="3">
+        <v>115</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="3"/>
-      <c r="N7" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="3"/>
-      <c r="P7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="1">
-        <v>115</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" t="s">
+      <c r="K8" s="2"/>
+      <c r="L8" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="3"/>
-      <c r="N8" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="3"/>
-      <c r="P8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>85</v>
       </c>
       <c r="C9" s="2">
         <v>63.511680399999022</v>
       </c>
-      <c r="D9" t="s">
-        <v>38</v>
+      <c r="D9" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="E9" s="2">
         <v>19.124744199914861</v>
       </c>
-      <c r="F9" t="s">
-        <v>13</v>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G9" s="2">
         <v>3.5954699851572507E-2</v>
       </c>
-      <c r="H9" t="s">
-        <v>13</v>
+      <c r="H9" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="I9" s="2">
         <v>0.33745929994620377</v>
       </c>
-      <c r="J9" t="s">
-        <v>39</v>
+      <c r="J9" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="K9" s="2">
         <v>0.37965720007196069</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="3">
+        <v>98</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="2">
-        <v>0.2181505998596549</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="K10" s="2"/>
+      <c r="L10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="2">
-        <v>5.3042500047013157E-2</v>
-      </c>
-      <c r="P9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="1">
-        <v>98</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" t="s">
+    </row>
+    <row r="11" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M10" s="3"/>
-      <c r="N10" t="s">
+      <c r="K11" s="2"/>
+      <c r="L11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="1">
-        <v>100</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" t="s">
+    </row>
+    <row r="12" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="3">
+        <v>102</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K11" s="3"/>
-      <c r="L11" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="3"/>
-      <c r="N11" t="s">
+      <c r="K12" s="2"/>
+      <c r="L12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="1">
-        <v>102</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" t="s">
+    </row>
+    <row r="13" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="3">
+        <v>115</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M12" s="3"/>
-      <c r="N12" t="s">
-        <v>56</v>
-      </c>
-      <c r="O12" s="3"/>
-      <c r="P12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="1">
-        <v>115</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" t="s">
+      <c r="K13" s="2"/>
+      <c r="L13" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" s="3"/>
-      <c r="L13" t="s">
-        <v>59</v>
-      </c>
-      <c r="M13" s="3"/>
-      <c r="N13" t="s">
-        <v>60</v>
-      </c>
-      <c r="O13" s="3"/>
-      <c r="P13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="1">
+      <c r="B14" s="3">
         <v>85</v>
       </c>
       <c r="C14" s="2">
         <v>46.317853400018073</v>
       </c>
-      <c r="D14" t="s">
-        <v>63</v>
+      <c r="D14" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="E14" s="2">
         <v>19.155991000123318</v>
       </c>
-      <c r="F14" t="s">
-        <v>13</v>
+      <c r="F14" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G14" s="2">
         <v>3.5835999995470047E-2</v>
       </c>
-      <c r="H14" t="s">
-        <v>13</v>
+      <c r="H14" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="I14" s="2">
         <v>0.29837689991109068</v>
       </c>
-      <c r="J14" t="s">
-        <v>64</v>
+      <c r="J14" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="K14" s="2">
         <v>0.3349947000388056</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="3">
+        <v>98</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="2">
-        <v>0.23779750009998679</v>
-      </c>
-      <c r="N14" t="s">
-        <v>66</v>
-      </c>
-      <c r="O14" s="2">
-        <v>5.5060999933630228E-2</v>
-      </c>
-      <c r="P14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="1">
-        <v>98</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" t="s">
+    </row>
+    <row r="16" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="3"/>
-      <c r="J15" t="s">
+      <c r="E16" s="2"/>
+      <c r="F16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K15" s="3"/>
-      <c r="L15" t="s">
+      <c r="K16" s="2"/>
+      <c r="L16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M15" s="3"/>
-      <c r="N15" t="s">
-        <v>70</v>
-      </c>
-      <c r="O15" s="3"/>
-      <c r="P15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="1">
-        <v>100</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" t="s">
+    </row>
+    <row r="17" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="3">
+        <v>102</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="3"/>
-      <c r="J16" t="s">
+      <c r="E17" s="2"/>
+      <c r="F17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" t="s">
+      <c r="K17" s="2"/>
+      <c r="L17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M16" s="3"/>
-      <c r="N16" t="s">
-        <v>74</v>
-      </c>
-      <c r="O16" s="3"/>
-      <c r="P16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="1">
-        <v>102</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" t="s">
+    </row>
+    <row r="18" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="3">
+        <v>115</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K17" s="3"/>
-      <c r="L17" t="s">
-        <v>77</v>
-      </c>
-      <c r="M17" s="3"/>
-      <c r="N17" t="s">
-        <v>78</v>
-      </c>
-      <c r="O17" s="3"/>
-      <c r="P17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="1">
-        <v>115</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" t="s">
+      <c r="K18" s="2"/>
+      <c r="L18" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="3"/>
-      <c r="J18" t="s">
-        <v>80</v>
-      </c>
-      <c r="K18" s="3"/>
-      <c r="L18" t="s">
-        <v>80</v>
-      </c>
-      <c r="M18" s="3"/>
-      <c r="N18" t="s">
-        <v>81</v>
-      </c>
-      <c r="O18" s="3"/>
-      <c r="P18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="1">
+      <c r="B19" s="3">
         <v>85</v>
       </c>
       <c r="C19" s="2">
         <v>57.062711199978366</v>
       </c>
-      <c r="D19" t="s">
-        <v>84</v>
+      <c r="D19" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="E19" s="2">
         <v>10.600846600020301</v>
       </c>
-      <c r="F19" t="s">
-        <v>13</v>
+      <c r="F19" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G19" s="2">
         <v>3.5606800112873323E-2</v>
       </c>
-      <c r="H19" t="s">
-        <v>13</v>
+      <c r="H19" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="I19" s="2">
         <v>0.309934499906376</v>
       </c>
-      <c r="J19" t="s">
-        <v>85</v>
+      <c r="J19" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="K19" s="2">
         <v>0.28068899991922081</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="3">
+        <v>98</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M19" s="2">
-        <v>0.20499200001358989</v>
-      </c>
-      <c r="N19" t="s">
-        <v>87</v>
-      </c>
-      <c r="O19" s="2">
-        <v>5.0298599991947412E-2</v>
-      </c>
-      <c r="P19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="1">
+    </row>
+    <row r="21" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="3">
+        <v>100</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="3">
+        <v>102</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="3">
+        <v>115</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="3"/>
-      <c r="H20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="3"/>
-      <c r="J20" t="s">
-        <v>89</v>
-      </c>
-      <c r="K20" s="3"/>
-      <c r="L20" t="s">
-        <v>90</v>
-      </c>
-      <c r="M20" s="3"/>
-      <c r="N20" t="s">
-        <v>91</v>
-      </c>
-      <c r="O20" s="3"/>
-      <c r="P20" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="1">
+      <c r="E23" s="2"/>
+      <c r="F23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" t="s">
-        <v>94</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" t="s">
-        <v>95</v>
-      </c>
-      <c r="M21" s="3"/>
-      <c r="N21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O21" s="3"/>
-      <c r="P21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="1">
+    </row>
+    <row r="24" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="3"/>
-      <c r="J22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K22" s="3"/>
-      <c r="L22" t="s">
-        <v>99</v>
-      </c>
-      <c r="M22" s="3"/>
-      <c r="N22" t="s">
-        <v>100</v>
-      </c>
-      <c r="O22" s="3"/>
-      <c r="P22" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="1">
-        <v>115</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="3"/>
-      <c r="J23" t="s">
-        <v>103</v>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" t="s">
-        <v>104</v>
-      </c>
-      <c r="M23" s="3"/>
-      <c r="N23" t="s">
-        <v>105</v>
-      </c>
-      <c r="O23" s="3"/>
-      <c r="P23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="1">
+      <c r="B24" s="3">
         <v>85</v>
       </c>
       <c r="C24" s="2">
         <v>57.467205699998892</v>
       </c>
-      <c r="D24" t="s">
-        <v>107</v>
+      <c r="D24" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="E24" s="2">
         <v>17.339781300164759</v>
       </c>
-      <c r="F24" t="s">
-        <v>13</v>
+      <c r="F24" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G24" s="2">
         <v>4.3367500184103847E-2</v>
       </c>
-      <c r="H24" t="s">
-        <v>13</v>
+      <c r="H24" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="I24" s="2">
         <v>0.31430059997364879</v>
       </c>
-      <c r="J24" t="s">
-        <v>108</v>
+      <c r="J24" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="K24" s="2">
         <v>0.2823901001829654</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="3">
+        <v>98</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M24" s="2">
-        <v>0.18934719986282289</v>
-      </c>
-      <c r="N24" t="s">
-        <v>110</v>
-      </c>
-      <c r="O24" s="2">
-        <v>4.4683499960228801E-2</v>
-      </c>
-      <c r="P24" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="1">
-        <v>98</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" t="s">
+    </row>
+    <row r="26" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="3">
+        <v>100</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="H25" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" t="s">
+      <c r="E26" s="2"/>
+      <c r="F26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="K25" s="3"/>
-      <c r="L25" t="s">
+      <c r="K26" s="2"/>
+      <c r="L26" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M25" s="3"/>
-      <c r="N25" t="s">
-        <v>114</v>
-      </c>
-      <c r="O25" s="3"/>
-      <c r="P25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="1">
-        <v>100</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" t="s">
+    </row>
+    <row r="27" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="3">
+        <v>102</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26" t="s">
+      <c r="E27" s="2"/>
+      <c r="F27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" t="s">
+      <c r="K27" s="2"/>
+      <c r="L27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="M26" s="3"/>
-      <c r="N26" t="s">
-        <v>118</v>
-      </c>
-      <c r="O26" s="3"/>
-      <c r="P26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="1">
-        <v>102</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" t="s">
+    </row>
+    <row r="28" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="3">
+        <v>115</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="3"/>
-      <c r="H27" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="3"/>
-      <c r="J27" t="s">
+      <c r="E28" s="2"/>
+      <c r="F28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" t="s">
+      <c r="K28" s="2"/>
+      <c r="L28" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="M27" s="3"/>
-      <c r="N27" t="s">
-        <v>122</v>
-      </c>
-      <c r="O27" s="3"/>
-      <c r="P27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="1">
-        <v>115</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" t="s">
+    </row>
+    <row r="29" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E28" s="3"/>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="3"/>
-      <c r="H28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="3"/>
-      <c r="J28" t="s">
-        <v>124</v>
-      </c>
-      <c r="K28" s="3"/>
-      <c r="L28" t="s">
-        <v>125</v>
-      </c>
-      <c r="M28" s="3"/>
-      <c r="N28" t="s">
-        <v>126</v>
-      </c>
-      <c r="O28" s="3"/>
-      <c r="P28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B29" s="1">
+      <c r="B29" s="3">
         <v>85</v>
       </c>
       <c r="C29" s="2">
         <v>59.466709400061518</v>
       </c>
-      <c r="D29" t="s">
-        <v>128</v>
+      <c r="D29" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="E29" s="2">
         <v>7.6415897998958826</v>
       </c>
-      <c r="F29" t="s">
-        <v>13</v>
+      <c r="F29" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G29" s="2">
         <v>3.8662499981001019E-2</v>
       </c>
-      <c r="H29" t="s">
-        <v>13</v>
+      <c r="H29" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="I29" s="2">
         <v>0.32897969987243408</v>
       </c>
-      <c r="J29" t="s">
-        <v>129</v>
+      <c r="J29" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="K29" s="2">
         <v>0.26394580001942808</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="3">
+        <v>98</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K30" s="2"/>
+      <c r="L30" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="M29" s="2">
+    </row>
+    <row r="31" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="3">
+        <v>100</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="3">
+        <v>102</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K32" s="2"/>
+      <c r="L32" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="3">
+        <v>115</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="3">
+        <v>85</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.25195700000040228</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="2">
+        <v>6.4450300065800548E-2</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6"/>
+      <c r="B40" s="3">
+        <v>98</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6"/>
+      <c r="B41" s="3">
+        <v>100</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="6"/>
+      <c r="B42" s="3">
+        <v>102</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7"/>
+      <c r="B43" s="3">
+        <v>115</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" s="3">
+        <v>85</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.2181505998596549</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E44" s="2">
+        <v>5.3042500047013157E-2</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="6"/>
+      <c r="B45" s="3">
+        <v>98</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6"/>
+      <c r="B46" s="3">
+        <v>100</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="6"/>
+      <c r="B47" s="3">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7"/>
+      <c r="B48" s="3">
+        <v>115</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="3">
+        <v>85</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.23779750009998679</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="2">
+        <v>5.5060999933630228E-2</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6"/>
+      <c r="B50" s="3">
+        <v>98</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="6"/>
+      <c r="B51" s="3">
+        <v>100</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="6"/>
+      <c r="B52" s="3">
+        <v>102</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="7"/>
+      <c r="B53" s="3">
+        <v>115</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" s="3">
+        <v>85</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0.20499200001358989</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" s="2">
+        <v>5.0298599991947412E-2</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="6"/>
+      <c r="B55" s="3">
+        <v>98</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="6"/>
+      <c r="B56" s="3">
+        <v>100</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="6"/>
+      <c r="B57" s="3">
+        <v>102</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="7"/>
+      <c r="B58" s="3">
+        <v>115</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B59" s="3">
+        <v>85</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0.18934719986282289</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E59" s="2">
+        <v>4.4683499960228801E-2</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="6"/>
+      <c r="B60" s="3">
+        <v>98</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="6"/>
+      <c r="B61" s="3">
+        <v>100</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="6"/>
+      <c r="B62" s="3">
+        <v>102</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="7"/>
+      <c r="B63" s="3">
+        <v>115</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" s="3">
+        <v>85</v>
+      </c>
+      <c r="C64" s="2">
         <v>0.20916810003109279</v>
       </c>
-      <c r="N29" t="s">
+      <c r="D64" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E64" s="2">
+        <v>4.9641999881714582E-2</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="6"/>
+      <c r="B65" s="3">
+        <v>98</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="O29" s="2">
-        <v>4.9641999881714582E-2</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="E65" s="2"/>
+      <c r="F65" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="1">
-        <v>98</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" t="s">
-        <v>132</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="3"/>
-      <c r="H30" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="3"/>
-      <c r="J30" t="s">
-        <v>133</v>
-      </c>
-      <c r="K30" s="3"/>
-      <c r="L30" t="s">
-        <v>134</v>
-      </c>
-      <c r="M30" s="3"/>
-      <c r="N30" t="s">
+    <row r="66" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="6"/>
+      <c r="B66" s="3">
+        <v>100</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="O30" s="3"/>
-      <c r="P30" t="s">
+      <c r="E66" s="2"/>
+      <c r="F66" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="1">
-        <v>100</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" t="s">
-        <v>136</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="3"/>
-      <c r="H31" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="3"/>
-      <c r="J31" t="s">
-        <v>137</v>
-      </c>
-      <c r="K31" s="3"/>
-      <c r="L31" t="s">
-        <v>138</v>
-      </c>
-      <c r="M31" s="3"/>
-      <c r="N31" t="s">
+    <row r="67" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="6"/>
+      <c r="B67" s="3">
+        <v>102</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="O31" s="3"/>
-      <c r="P31" t="s">
+      <c r="E67" s="2"/>
+      <c r="F67" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="1">
-        <v>102</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="3"/>
-      <c r="J32" t="s">
-        <v>141</v>
-      </c>
-      <c r="K32" s="3"/>
-      <c r="L32" t="s">
-        <v>142</v>
-      </c>
-      <c r="M32" s="3"/>
-      <c r="N32" t="s">
+    <row r="68" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="7"/>
+      <c r="B68" s="3">
+        <v>115</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="O32" s="3"/>
-      <c r="P32" t="s">
+      <c r="E68" s="2"/>
+      <c r="F68" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="1">
-        <v>115</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" t="s">
-        <v>144</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="3"/>
-      <c r="J33" t="s">
-        <v>145</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" t="s">
-        <v>146</v>
-      </c>
-      <c r="M33" s="3"/>
-      <c r="N33" t="s">
-        <v>147</v>
-      </c>
-      <c r="O33" s="3"/>
-      <c r="P33" t="s">
-        <v>147</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="O24:O28"/>
-    <mergeCell ref="K9:K13"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="M9:M13"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E9:E13"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="K29:K33"/>
-    <mergeCell ref="O29:O33"/>
-    <mergeCell ref="E19:E23"/>
-    <mergeCell ref="G19:G23"/>
-    <mergeCell ref="O4:O8"/>
-    <mergeCell ref="M24:M28"/>
-    <mergeCell ref="C19:C23"/>
-    <mergeCell ref="M29:M33"/>
-    <mergeCell ref="O14:O18"/>
-    <mergeCell ref="K4:K8"/>
-    <mergeCell ref="G9:G13"/>
-    <mergeCell ref="O9:O13"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="M19:M23"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="K24:K28"/>
-    <mergeCell ref="O19:O23"/>
-    <mergeCell ref="E14:E18"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="I19:I23"/>
-    <mergeCell ref="M14:M18"/>
-    <mergeCell ref="A19:A23"/>
-    <mergeCell ref="K19:K23"/>
+  <mergeCells count="61">
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A59:A63"/>
+    <mergeCell ref="A64:A68"/>
     <mergeCell ref="A29:A33"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="K1:L1"/>
@@ -2144,20 +2361,57 @@
     <mergeCell ref="I9:I13"/>
     <mergeCell ref="I29:I33"/>
     <mergeCell ref="A24:A28"/>
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="I4:I8"/>
     <mergeCell ref="I14:I18"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A9:A13"/>
-    <mergeCell ref="M4:M8"/>
     <mergeCell ref="C9:C13"/>
     <mergeCell ref="K14:K18"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="G4:G8"/>
     <mergeCell ref="G24:G28"/>
-    <mergeCell ref="I24:I28"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="I19:I23"/>
+    <mergeCell ref="C49:C53"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="K19:K23"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C39:C43"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="G14:G18"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="E49:E53"/>
+    <mergeCell ref="K4:K8"/>
+    <mergeCell ref="G9:G13"/>
+    <mergeCell ref="E44:E48"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C54:C58"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="K24:K28"/>
+    <mergeCell ref="E54:E58"/>
+    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="I24:I28"/>
+    <mergeCell ref="E59:E63"/>
+    <mergeCell ref="K9:K13"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E9:E13"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="K29:K33"/>
+    <mergeCell ref="E64:E68"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="G19:G23"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="C59:C63"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="C64:C68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
